--- a/PROPERTIES/PRIANA/PRIANA 2025.xlsx
+++ b/PROPERTIES/PRIANA/PRIANA 2025.xlsx
@@ -5,13 +5,14 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="MAY" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="JUNE" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="JULY" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="AUG" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="106">
   <si>
     <t xml:space="preserve">TEL: 0703759351 / 0723575686</t>
   </si>
@@ -338,6 +339,9 @@
   </si>
   <si>
     <t xml:space="preserve">SECURITY/CAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VACANT</t>
   </si>
 </sst>
 </file>
@@ -353,7 +357,7 @@
     <numFmt numFmtId="169" formatCode="0.00"/>
     <numFmt numFmtId="170" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -517,6 +521,22 @@
       <family val="1"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10.5"/>
+      <color rgb="FF008000"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -589,7 +609,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="98">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -951,6 +971,34 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="170" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4732,4 +4780,931 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:L55"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="59" width="8.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="59" width="23.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="59" width="19.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="59" width="16.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="59" width="13.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="59" width="12.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="59" width="13.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="59" width="17.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="59" width="15.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="59" width="21.44"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="11" style="59" width="8.54"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="60" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="63" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="62"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="62" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="62" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="62" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="64" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="66" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="67" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="68" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="69" t="n">
+        <v>13000</v>
+      </c>
+      <c r="E7" s="69"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="91"/>
+      <c r="H7" s="92" t="n">
+        <v>13000</v>
+      </c>
+      <c r="I7" s="93"/>
+      <c r="J7" s="67"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="61" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="69" t="n">
+        <v>14000</v>
+      </c>
+      <c r="E8" s="69"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="91"/>
+      <c r="H8" s="92"/>
+      <c r="I8" s="91"/>
+      <c r="J8" s="67"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="71" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="73" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E9" s="73"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="95" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I9" s="91"/>
+      <c r="J9" s="67"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="69" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E10" s="69"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="91"/>
+      <c r="H10" s="92" t="n">
+        <v>16000</v>
+      </c>
+      <c r="I10" s="91"/>
+      <c r="J10" s="75"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="61" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="67" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="69" t="n">
+        <v>19000</v>
+      </c>
+      <c r="E11" s="69"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="91"/>
+      <c r="H11" s="92" t="n">
+        <v>19000</v>
+      </c>
+      <c r="I11" s="91"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="76" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="59" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" s="69" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E12" s="77"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="91" t="n">
+        <v>36000</v>
+      </c>
+      <c r="H12" s="92"/>
+      <c r="I12" s="91"/>
+      <c r="J12" s="67"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="67" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="68" t="n">
+        <v>719808472</v>
+      </c>
+      <c r="D13" s="69" t="n">
+        <v>15500</v>
+      </c>
+      <c r="E13" s="69"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="91"/>
+      <c r="H13" s="92"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="67"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="67" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="68" t="n">
+        <v>713445149</v>
+      </c>
+      <c r="D14" s="69" t="n">
+        <v>17000</v>
+      </c>
+      <c r="E14" s="69"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="91"/>
+      <c r="H14" s="92"/>
+      <c r="I14" s="91"/>
+      <c r="J14" s="67"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="61" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="67" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="78" t="n">
+        <v>719316193</v>
+      </c>
+      <c r="D15" s="69" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E15" s="69"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="91"/>
+      <c r="H15" s="92" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I15" s="91"/>
+      <c r="J15" s="79"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="61" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="67" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="68" t="n">
+        <v>719347383</v>
+      </c>
+      <c r="D16" s="69" t="n">
+        <v>19000</v>
+      </c>
+      <c r="E16" s="69"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="91"/>
+      <c r="H16" s="92" t="n">
+        <v>19000</v>
+      </c>
+      <c r="I16" s="91"/>
+      <c r="J16" s="67"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="61" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="67" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" s="68" t="n">
+        <v>112980050</v>
+      </c>
+      <c r="D17" s="69" t="n">
+        <v>15500</v>
+      </c>
+      <c r="E17" s="69"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="91"/>
+      <c r="H17" s="92" t="n">
+        <v>15500</v>
+      </c>
+      <c r="I17" s="91"/>
+      <c r="J17" s="75"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="61" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="67" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="68" t="n">
+        <v>715934101</v>
+      </c>
+      <c r="D18" s="69" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E18" s="69"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="91"/>
+      <c r="H18" s="92" t="n">
+        <v>16000</v>
+      </c>
+      <c r="I18" s="91"/>
+      <c r="J18" s="67"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="61" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="67" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="68" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="69" t="n">
+        <v>19000</v>
+      </c>
+      <c r="E19" s="69"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="91"/>
+      <c r="H19" s="92"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="75"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="61" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="67" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="61" t="n">
+        <v>705326359</v>
+      </c>
+      <c r="D20" s="80" t="n">
+        <v>19000</v>
+      </c>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="96"/>
+      <c r="H20" s="97" t="n">
+        <v>19000</v>
+      </c>
+      <c r="I20" s="91"/>
+      <c r="J20" s="82"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="70" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="71" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" s="78" t="n">
+        <v>711620882</v>
+      </c>
+      <c r="D21" s="73" t="n">
+        <v>15500</v>
+      </c>
+      <c r="E21" s="73"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="94"/>
+      <c r="H21" s="95" t="n">
+        <v>15500</v>
+      </c>
+      <c r="I21" s="91"/>
+      <c r="J21" s="79"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="61" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="67" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" s="68" t="n">
+        <v>796152241</v>
+      </c>
+      <c r="D22" s="69" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E22" s="69"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="91"/>
+      <c r="H22" s="92" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I22" s="91" t="n">
+        <v>11000</v>
+      </c>
+      <c r="J22" s="67"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="67" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="68" t="n">
+        <v>702159772</v>
+      </c>
+      <c r="D23" s="69" t="n">
+        <v>21000</v>
+      </c>
+      <c r="E23" s="69"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="91"/>
+      <c r="H23" s="92" t="n">
+        <v>21000</v>
+      </c>
+      <c r="I23" s="91"/>
+      <c r="J23" s="75"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="61" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="67" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" s="68" t="n">
+        <v>714710386</v>
+      </c>
+      <c r="D24" s="69" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E24" s="65"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="91"/>
+      <c r="H24" s="92" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I24" s="91"/>
+      <c r="J24" s="75"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="61" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="67" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="68" t="n">
+        <v>727468700</v>
+      </c>
+      <c r="D25" s="69" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E25" s="69"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="91"/>
+      <c r="H25" s="92" t="n">
+        <v>16000</v>
+      </c>
+      <c r="I25" s="91"/>
+      <c r="J25" s="75"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="61" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="67" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="68" t="n">
+        <v>712953086</v>
+      </c>
+      <c r="D26" s="69" t="n">
+        <v>17450</v>
+      </c>
+      <c r="E26" s="69"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="91"/>
+      <c r="H26" s="92" t="n">
+        <v>17450</v>
+      </c>
+      <c r="I26" s="91"/>
+      <c r="J26" s="67"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="61" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="67" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="68" t="n">
+        <v>714738962</v>
+      </c>
+      <c r="D27" s="69" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E27" s="69"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="91"/>
+      <c r="H27" s="92" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I27" s="91"/>
+      <c r="J27" s="75"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" s="67" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="83"/>
+      <c r="D28" s="69" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E28" s="69"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="91"/>
+      <c r="H28" s="92"/>
+      <c r="I28" s="91"/>
+      <c r="J28" s="84"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="61" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="67" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" s="68" t="n">
+        <v>729365857</v>
+      </c>
+      <c r="D29" s="69" t="n">
+        <v>16250</v>
+      </c>
+      <c r="E29" s="69"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="91"/>
+      <c r="H29" s="92" t="n">
+        <v>16250</v>
+      </c>
+      <c r="I29" s="91"/>
+      <c r="J29" s="85"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="62"/>
+      <c r="B30" s="62"/>
+      <c r="C30" s="62"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="91" t="n">
+        <f aca="false">SUM(G7:G29)</f>
+        <v>36000</v>
+      </c>
+      <c r="H30" s="92" t="n">
+        <f aca="false">SUM(H7:H29)</f>
+        <v>303700</v>
+      </c>
+      <c r="I30" s="91"/>
+      <c r="J30" s="67"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C31" s="86" t="s">
+        <v>101</v>
+      </c>
+      <c r="E31" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="67" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="67"/>
+      <c r="D32" s="67"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="67" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="81"/>
+      <c r="D33" s="81"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="61" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" s="67"/>
+      <c r="D34" s="67"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+    </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="61"/>
+      <c r="C35" s="67"/>
+      <c r="D35" s="67"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="76"/>
+      <c r="I35" s="76"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+    </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D36" s="76"/>
+      <c r="E36" s="76"/>
+      <c r="F36" s="76"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="76"/>
+      <c r="I36" s="76"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+    </row>
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="1"/>
+      <c r="C37" s="76"/>
+      <c r="D37" s="76"/>
+      <c r="E37" s="76"/>
+      <c r="F37" s="76"/>
+      <c r="G37" s="88"/>
+      <c r="H37" s="89"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+    </row>
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="1"/>
+      <c r="C38" s="76"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="76"/>
+      <c r="F38" s="76"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+    </row>
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="86" t="s">
+        <v>103</v>
+      </c>
+      <c r="C39" s="76"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="76"/>
+      <c r="F39" s="76"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+    </row>
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="76"/>
+      <c r="F40" s="76"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+    </row>
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D41" s="90"/>
+      <c r="E41" s="90"/>
+      <c r="F41" s="90"/>
+      <c r="G41" s="90"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+    </row>
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D42" s="76"/>
+      <c r="E42" s="76"/>
+      <c r="F42" s="76"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+    </row>
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D43" s="76"/>
+      <c r="E43" s="76"/>
+      <c r="F43" s="76"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+    </row>
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D44" s="76"/>
+      <c r="E44" s="90"/>
+      <c r="F44" s="76"/>
+      <c r="H44" s="89"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D45" s="76"/>
+      <c r="E45" s="76"/>
+      <c r="F45" s="76"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+    </row>
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="H46" s="89"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+    </row>
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+    </row>
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="76"/>
+      <c r="H48" s="90"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="90"/>
+      <c r="H49" s="76"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+    </row>
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="I50" s="76"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+    </row>
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="J51" s="90"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+    </row>
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J52" s="76"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+    </row>
+    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+    </row>
+    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+    </row>
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="A30:C30"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>